--- a/Configs/GameConfig/Datas/LevelSpawnConfig.xlsx
+++ b/Configs/GameConfig/Datas/LevelSpawnConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -542,7 +542,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>怪物ID(MonsterConfig.Id;2/3待迁)</t>
+          <t>怪物ID(MonsterConfig.Id;M6 垂直切片全用花果山猴子,旧 Monster_2/3 迁入后改回)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>2000</v>
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>2000</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>2000</v>
@@ -898,7 +898,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>2000</v>
@@ -925,7 +925,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>2000</v>
@@ -952,7 +952,7 @@
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>2000</v>
@@ -979,7 +979,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>2000</v>
@@ -1006,7 +1006,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>2000</v>
@@ -1033,7 +1033,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>2000</v>
@@ -1060,7 +1060,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>2000</v>
@@ -1087,7 +1087,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>2000</v>
@@ -1114,7 +1114,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>2000</v>
@@ -1141,7 +1141,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>2000</v>
@@ -1168,7 +1168,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>2000</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>3000</v>
@@ -1222,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>3000</v>
@@ -1249,7 +1249,7 @@
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>3000</v>
@@ -1276,7 +1276,7 @@
         <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>3000</v>
@@ -1303,7 +1303,7 @@
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>3000</v>
@@ -1330,7 +1330,7 @@
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>3000</v>
@@ -1357,7 +1357,7 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>3000</v>
@@ -1384,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>3000</v>
@@ -1411,7 +1411,7 @@
         <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>3000</v>
@@ -1438,7 +1438,7 @@
         <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>3000</v>
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
         <v>3000</v>
@@ -1492,7 +1492,7 @@
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
         <v>3000</v>
@@ -1519,7 +1519,7 @@
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>3000</v>
@@ -1546,7 +1546,7 @@
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>3000</v>
@@ -1573,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>3000</v>
@@ -1600,7 +1600,7 @@
         <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>4500</v>
@@ -1627,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v>4500</v>
@@ -1654,7 +1654,7 @@
         <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>4500</v>
@@ -1681,7 +1681,7 @@
         <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>4500</v>
@@ -1708,7 +1708,7 @@
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>4500</v>
@@ -1735,7 +1735,7 @@
         <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>4500</v>
